--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T05:20:25+00:00</t>
+    <t>2026-09-28T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:16:57+00:00</t>
+    <t>2026-09-28T10:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:26:56+00:00</t>
+    <t>2026-09-28T11:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:29:30+00:00</t>
+    <t>2026-09-28T12:11:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:11:39+00:00</t>
+    <t>2026-09-28T20:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T20:57:11+00:00</t>
+    <t>2026-09-28T21:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:01:12+00:00</t>
+    <t>2026-09-30T11:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:29:35+00:00</t>
+    <t>2026-10-01T05:55:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T05:55:59+00:00</t>
+    <t>2026-10-01T06:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
+++ b/ci-build/ConceptMapOnkoTherapyGoalTypeSct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
